--- a/Result/profitability/1321.xlsx
+++ b/Result/profitability/1321.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,16 +669,16 @@
         <v>-0.12</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1625</v>
+        <v>-0.07250000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>7.703749999999999</v>
+        <v>8.73625</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.01</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.15</v>
+        <v>-0.07625</v>
       </c>
       <c r="N3" t="n">
-        <v>8.133750000000001</v>
+        <v>8.34125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.04</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1475</v>
+        <v>-0.045</v>
       </c>
       <c r="N4" t="n">
-        <v>7.72625</v>
+        <v>8.102499999999999</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-1.11</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.26</v>
+        <v>-0.13375</v>
       </c>
       <c r="N5" t="n">
-        <v>6.52625</v>
+        <v>6.920000000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.11</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2237500000000001</v>
+        <v>-0.13125</v>
       </c>
       <c r="N6" t="n">
-        <v>6.12125</v>
+        <v>7.09375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.12</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1925</v>
+        <v>-0.0525</v>
       </c>
       <c r="N7" t="n">
-        <v>6.98875</v>
+        <v>7.58625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.26</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.09625000000000003</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>7.49625</v>
+        <v>7.4675</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>-0.03</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.09375000000000003</v>
+        <v>-0.09375</v>
       </c>
       <c r="N10" t="n">
         <v>6.815</v>
@@ -2026,7 +2026,7 @@
         <v>-0.14</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.03250000000000003</v>
+        <v>-0.0325</v>
       </c>
       <c r="N13" t="n">
         <v>7.0375</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1024</v>
+      </c>
+      <c r="D75" t="n">
+        <v>904</v>
+      </c>
+      <c r="E75" t="n">
+        <v>120</v>
+      </c>
+      <c r="F75" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="G75" t="n">
+        <v>10</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1.02%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>193</v>
+      </c>
+      <c r="J75" t="n">
+        <v>203</v>
+      </c>
+      <c r="K75" t="n">
+        <v>136</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.07124999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>8.188749999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2.8125</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.2300000000000004</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.0192147034252298</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-2.525</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.3667054714784634</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
